--- a/LED/Display.xlsx
+++ b/LED/Display.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bb/Repo/GitHub/Vape/LED/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8929E53D-CF0C-FF48-8772-3C298B615A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D6E512C-E375-0941-A525-593550A448C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23980" yWindow="1540" windowWidth="27640" windowHeight="16680" xr2:uid="{FA0983D9-37EC-9845-A33A-90CFAB0B6699}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="19">
   <si>
     <t>BATT</t>
   </si>
@@ -45,6 +45,54 @@
   </si>
   <si>
     <t>%</t>
+  </si>
+  <si>
+    <t>LLLLL</t>
+  </si>
+  <si>
+    <t>LLLLH</t>
+  </si>
+  <si>
+    <t>LLLHL</t>
+  </si>
+  <si>
+    <t>LLLHH</t>
+  </si>
+  <si>
+    <t>LLHLL</t>
+  </si>
+  <si>
+    <t>LLHLH</t>
+  </si>
+  <si>
+    <t>LLHHL</t>
+  </si>
+  <si>
+    <t>LLHHH</t>
+  </si>
+  <si>
+    <t>LHLLL</t>
+  </si>
+  <si>
+    <t>LHLLH</t>
+  </si>
+  <si>
+    <t>LHLHL</t>
+  </si>
+  <si>
+    <t>LHLHH</t>
+  </si>
+  <si>
+    <t>LHHLL</t>
+  </si>
+  <si>
+    <t>LHHLH</t>
+  </si>
+  <si>
+    <t>LHHHL</t>
+  </si>
+  <si>
+    <t>LHHHH</t>
   </si>
 </sst>
 </file>
@@ -559,8 +607,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2">
-        <v>0</v>
+      <c r="A1" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -659,8 +707,8 @@
       </c>
     </row>
     <row r="6" spans="1:10" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2">
-        <v>1</v>
+      <c r="A6" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>0</v>
@@ -759,8 +807,8 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="2">
-        <v>2</v>
+      <c r="A11" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>0</v>
@@ -859,8 +907,8 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="2">
-        <v>3</v>
+      <c r="A16" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>0</v>
@@ -959,8 +1007,8 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="2">
-        <v>4</v>
+      <c r="A21" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>0</v>
@@ -1059,8 +1107,8 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="2">
-        <v>5</v>
+      <c r="A26" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>0</v>
@@ -1159,8 +1207,8 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="2">
-        <v>6</v>
+      <c r="A31" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>0</v>
@@ -1259,8 +1307,8 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="2">
-        <v>7</v>
+      <c r="A36" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>0</v>
@@ -1359,8 +1407,8 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="2">
-        <v>8</v>
+      <c r="A41" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>0</v>
@@ -1459,8 +1507,8 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="2">
-        <v>9</v>
+      <c r="A46" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>0</v>
@@ -1559,8 +1607,8 @@
       </c>
     </row>
     <row r="51" spans="1:10" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="2">
-        <v>10</v>
+      <c r="A51" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>0</v>
@@ -1659,8 +1707,8 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="2">
-        <v>11</v>
+      <c r="A56" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>0</v>
@@ -1759,8 +1807,8 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="2">
-        <v>12</v>
+      <c r="A61" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>0</v>
@@ -1859,8 +1907,8 @@
       </c>
     </row>
     <row r="66" spans="1:10" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="2">
-        <v>13</v>
+      <c r="A66" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>0</v>
@@ -1959,8 +2007,8 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="2">
-        <v>14</v>
+      <c r="A71" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>0</v>
@@ -2059,8 +2107,8 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="2">
-        <v>15</v>
+      <c r="A76" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>0</v>
